--- a/datum/map_data.xlsx
+++ b/datum/map_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuyangao\Nutstore\1\我的坚果云\硕士\项目\24_nicotine\datum\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuyangao\Desktop\25_nicotine\datum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A24E46-305B-4448-AE1A-B190170A0DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42292319-4454-4AC8-B4EE-9C2FEA1502A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -537,7 +537,7 @@
     <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -595,6 +595,19 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -618,7 +631,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -672,6 +685,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -12016,143 +12038,143 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="80" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="3" t="s">
+    <row r="80" spans="1:46" s="19" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B80" s="10">
+      <c r="B80" s="20">
         <v>21</v>
       </c>
-      <c r="C80" s="10">
-        <v>1</v>
-      </c>
-      <c r="D80" s="18">
+      <c r="C80" s="20">
+        <v>1</v>
+      </c>
+      <c r="D80" s="21">
         <v>4</v>
       </c>
-      <c r="E80" s="18">
+      <c r="E80" s="21">
         <v>3</v>
       </c>
-      <c r="F80" s="10">
+      <c r="F80" s="20">
         <v>3</v>
       </c>
-      <c r="G80" s="10">
+      <c r="G80" s="20">
         <v>25</v>
       </c>
-      <c r="H80" s="1">
+      <c r="H80" s="19">
         <v>75</v>
       </c>
-      <c r="I80" s="3">
+      <c r="I80" s="19">
         <v>70</v>
       </c>
-      <c r="J80" s="3">
-        <v>0</v>
-      </c>
-      <c r="K80" s="1">
-        <v>2</v>
-      </c>
-      <c r="L80" s="3">
-        <v>1</v>
-      </c>
-      <c r="M80" s="1">
+      <c r="J80" s="19">
+        <v>0</v>
+      </c>
+      <c r="K80" s="19">
+        <v>2</v>
+      </c>
+      <c r="L80" s="19">
+        <v>1</v>
+      </c>
+      <c r="M80" s="19">
         <v>5.83</v>
       </c>
-      <c r="N80" s="1">
+      <c r="N80" s="19">
         <v>2.36</v>
       </c>
-      <c r="O80" s="1">
+      <c r="O80" s="19">
         <v>0.32</v>
       </c>
-      <c r="P80" s="1">
+      <c r="P80" s="19">
         <v>0.42</v>
       </c>
-      <c r="Q80" s="1">
+      <c r="Q80" s="19">
         <v>0.37</v>
       </c>
-      <c r="R80" s="1">
+      <c r="R80" s="19">
         <v>0.11</v>
       </c>
-      <c r="S80" s="1">
+      <c r="S80" s="19">
         <v>0.44</v>
       </c>
-      <c r="T80" s="1">
+      <c r="T80" s="19">
         <v>8.6300000000000008</v>
       </c>
-      <c r="U80" s="1">
+      <c r="U80" s="19">
         <v>0.87</v>
       </c>
-      <c r="V80" s="1">
+      <c r="V80" s="19">
         <v>0.1</v>
       </c>
-      <c r="W80" s="1">
+      <c r="W80" s="19">
         <v>0.15</v>
       </c>
-      <c r="X80" s="1">
+      <c r="X80" s="19">
         <v>0.11</v>
       </c>
-      <c r="Y80" s="1">
+      <c r="Y80" s="19">
         <v>0.14000000000000001</v>
       </c>
-      <c r="Z80" s="1">
+      <c r="Z80" s="19">
         <v>0.22</v>
       </c>
-      <c r="AA80" s="1">
+      <c r="AA80" s="19">
         <v>-0.24</v>
       </c>
-      <c r="AB80" s="1">
+      <c r="AB80" s="19">
         <v>-0.12</v>
       </c>
-      <c r="AC80" s="1">
+      <c r="AC80" s="19">
         <v>-0.24</v>
       </c>
-      <c r="AD80" s="1">
+      <c r="AD80" s="19">
         <v>-0.36</v>
       </c>
-      <c r="AE80" s="1">
+      <c r="AE80" s="19">
         <v>40</v>
       </c>
-      <c r="AF80" s="1">
+      <c r="AF80" s="19">
         <v>30</v>
       </c>
-      <c r="AG80" s="1">
+      <c r="AG80" s="19">
         <v>0.4</v>
       </c>
-      <c r="AH80" s="1">
+      <c r="AH80" s="19">
         <v>0.3</v>
       </c>
-      <c r="AI80" s="1">
+      <c r="AI80" s="19">
         <v>0.28000000000000003</v>
       </c>
-      <c r="AJ80" s="1">
+      <c r="AJ80" s="19">
         <v>-0.08</v>
       </c>
-      <c r="AK80" s="1">
+      <c r="AK80" s="19">
         <v>-0.09</v>
       </c>
-      <c r="AL80" s="1">
-        <v>0</v>
-      </c>
-      <c r="AM80" s="14">
+      <c r="AL80" s="19">
+        <v>0</v>
+      </c>
+      <c r="AM80" s="19">
         <v>0.92</v>
       </c>
-      <c r="AN80" s="14">
+      <c r="AN80" s="19">
         <v>0.7</v>
       </c>
-      <c r="AO80" s="14">
+      <c r="AO80" s="19">
         <v>0.64</v>
       </c>
-      <c r="AP80" s="14">
+      <c r="AP80" s="19">
         <v>0.78</v>
       </c>
-      <c r="AQ80" s="14">
+      <c r="AQ80" s="19">
         <v>0.81</v>
       </c>
-      <c r="AR80" s="14">
+      <c r="AR80" s="19">
         <v>0.75</v>
       </c>
-      <c r="AS80" s="14">
+      <c r="AS80" s="19">
         <v>0.9</v>
       </c>
-      <c r="AT80" s="14">
+      <c r="AT80" s="19">
         <v>0.75</v>
       </c>
     </row>

--- a/datum/map_data.xlsx
+++ b/datum/map_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuyangao\Desktop\25_nicotine\datum\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuyangao\Dropbox\24_nicotine\analysis\datum\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42292319-4454-4AC8-B4EE-9C2FEA1502A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A36760D0-11DD-4B34-9485-2C1CEA2CF117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,330 +31,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="208">
   <si>
     <t>FTND</t>
-  </si>
-  <si>
-    <t>蔡</t>
-  </si>
-  <si>
-    <t>戴</t>
-  </si>
-  <si>
-    <t>丁</t>
-  </si>
-  <si>
-    <t>葛</t>
-  </si>
-  <si>
-    <t>何</t>
-  </si>
-  <si>
-    <t>黄</t>
-  </si>
-  <si>
-    <t>连</t>
-  </si>
-  <si>
-    <t>钟</t>
-  </si>
-  <si>
-    <t>刘燕</t>
-  </si>
-  <si>
-    <t>缪</t>
-  </si>
-  <si>
-    <t>瞿</t>
-  </si>
-  <si>
-    <t>盛</t>
-  </si>
-  <si>
-    <t>武</t>
-  </si>
-  <si>
-    <t>叶</t>
-  </si>
-  <si>
-    <t>俞</t>
-  </si>
-  <si>
-    <t>包</t>
-  </si>
-  <si>
-    <t>崔</t>
-  </si>
-  <si>
-    <t>郑</t>
-  </si>
-  <si>
-    <t>孟</t>
-  </si>
-  <si>
-    <t>潘</t>
-  </si>
-  <si>
-    <t>涂</t>
-  </si>
-  <si>
-    <t>徐</t>
-  </si>
-  <si>
-    <t>杨</t>
-  </si>
-  <si>
-    <t>余</t>
-  </si>
-  <si>
-    <t>章</t>
-  </si>
-  <si>
-    <t>代</t>
-  </si>
-  <si>
-    <t>林一</t>
-  </si>
-  <si>
-    <t>彭</t>
-  </si>
-  <si>
-    <t>瓶瓶</t>
-  </si>
-  <si>
-    <t>圣云</t>
-  </si>
-  <si>
-    <t>梦婷</t>
-  </si>
-  <si>
-    <t>小冯</t>
-  </si>
-  <si>
-    <t>赵</t>
-  </si>
-  <si>
-    <t>租房</t>
-  </si>
-  <si>
-    <t>蒋</t>
-  </si>
-  <si>
-    <t>hyn</t>
-  </si>
-  <si>
-    <t>src</t>
-  </si>
-  <si>
-    <t>zzz</t>
-  </si>
-  <si>
-    <t>胡</t>
-  </si>
-  <si>
-    <t>林哲尔</t>
-  </si>
-  <si>
-    <t>林子萱</t>
-  </si>
-  <si>
-    <t>任</t>
-  </si>
-  <si>
-    <t>田</t>
-  </si>
-  <si>
-    <t>吴</t>
-  </si>
-  <si>
-    <t>严</t>
-  </si>
-  <si>
-    <t>张圣</t>
-  </si>
-  <si>
-    <t>www</t>
-  </si>
-  <si>
-    <t>yu</t>
-  </si>
-  <si>
-    <t>白小胖</t>
-  </si>
-  <si>
-    <t>邓宇</t>
-  </si>
-  <si>
-    <t>方天</t>
-  </si>
-  <si>
-    <t>黄嘉欣</t>
-  </si>
-  <si>
-    <t>李观正</t>
-  </si>
-  <si>
-    <t>王恪</t>
-  </si>
-  <si>
-    <t>李紫琳</t>
-  </si>
-  <si>
-    <t>寿懿婷</t>
-  </si>
-  <si>
-    <t>余晖武</t>
-  </si>
-  <si>
-    <t>张斯亚</t>
-  </si>
-  <si>
-    <t>陈华杰</t>
-  </si>
-  <si>
-    <t>李荣华</t>
-  </si>
-  <si>
-    <t>李亦涵</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 马文轩</t>
-  </si>
-  <si>
-    <t>张城玮</t>
-  </si>
-  <si>
-    <t>赵齐庆</t>
-  </si>
-  <si>
-    <t>李</t>
-  </si>
-  <si>
-    <t>唐</t>
-  </si>
-  <si>
-    <t>童</t>
-  </si>
-  <si>
-    <t>王</t>
-  </si>
-  <si>
-    <t>张万森</t>
-  </si>
-  <si>
-    <t>张言俊</t>
-  </si>
-  <si>
-    <t>aiduo</t>
-  </si>
-  <si>
-    <t>L#</t>
-  </si>
-  <si>
-    <t>Lawrence</t>
-  </si>
-  <si>
-    <t>XL</t>
-  </si>
-  <si>
-    <t>不想学英语</t>
-  </si>
-  <si>
-    <t>陈</t>
-  </si>
-  <si>
-    <t>煎饼</t>
-  </si>
-  <si>
-    <t>开水白菜</t>
-  </si>
-  <si>
-    <t>空白</t>
-  </si>
-  <si>
-    <t>梁凯</t>
-  </si>
-  <si>
-    <t>临床</t>
-  </si>
-  <si>
-    <t>飒sa</t>
-  </si>
-  <si>
-    <t>史沁栩</t>
-  </si>
-  <si>
-    <t>吴涛</t>
-  </si>
-  <si>
-    <t>小叶不长肉</t>
-  </si>
-  <si>
-    <t>郑泽锋</t>
-  </si>
-  <si>
-    <t>邓宇(v3)</t>
-  </si>
-  <si>
-    <t>李洋</t>
-  </si>
-  <si>
-    <t>喻</t>
-  </si>
-  <si>
-    <t>...</t>
-  </si>
-  <si>
-    <t>一</t>
-  </si>
-  <si>
-    <t>herkaide</t>
-  </si>
-  <si>
-    <t>HYX</t>
-  </si>
-  <si>
-    <t>robbie</t>
-  </si>
-  <si>
-    <t>star</t>
-  </si>
-  <si>
-    <t>wjz</t>
-  </si>
-  <si>
-    <t>xxx</t>
-  </si>
-  <si>
-    <t>东东</t>
-  </si>
-  <si>
-    <t>高贵</t>
-  </si>
-  <si>
-    <t>关真硕</t>
-  </si>
-  <si>
-    <t>冠宇</t>
-  </si>
-  <si>
-    <t>李万源</t>
-  </si>
-  <si>
-    <t>迷糊</t>
-  </si>
-  <si>
-    <t>勿忘我</t>
-  </si>
-  <si>
-    <t>徐桑</t>
-  </si>
-  <si>
-    <t>俞启越</t>
-  </si>
-  <si>
-    <t>朱小龙</t>
   </si>
   <si>
     <t>name</t>
@@ -528,6 +207,654 @@
     <t>smoke_quantify</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>001</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>002</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>003_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>004_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>005_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>006_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>007_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>008_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>009_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>010_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>010</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>012_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>013_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>014_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>015_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>016_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>017_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>018_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>019_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>020_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>021_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>022_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>023_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>024_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>025_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>026_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>027_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>028_210</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>029_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>030</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>032</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>033</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>034</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>035</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>036</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>037</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>038</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>039</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>040</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>041</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>042</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>043</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>044</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>045</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>046_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>047_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>048_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>049_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>050_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>051_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>052_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>053_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>054_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>055_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>056_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>057_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>058_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>059_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>060_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>061_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>062_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>063_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>064</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>065</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>066</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>068</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>069</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>070</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>072</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>073</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>075</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>077</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>078</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>079</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>080</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>081</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>082</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>083_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>084_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>085_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>086_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>087_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>088_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>089_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>090_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>091_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>092</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>093_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>094_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>095_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>096_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>097_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>098_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>099_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>100_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>101_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>102_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>103_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>104_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>105_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>106_</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>107_</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>108</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>109</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>110</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>111</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>112</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>113</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>114</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>115</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>116</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>117</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>118</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>119</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>120</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>121</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>122</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>123_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>124_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>125</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>126_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>127_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>128_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>129_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>130_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>131_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>132_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>133_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>134_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>135_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>136_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>137_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>138_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>139_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>140_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>141_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>142_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>143_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>144_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>145_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>146_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>147_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>148_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>149_</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>150</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>151_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>152</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>153</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>154</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>155</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>156</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>157</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>158</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>159</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>160</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>161</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>162</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>163</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>164</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>165</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>166</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>167</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -537,7 +864,7 @@
     <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -595,19 +922,6 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -631,7 +945,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -687,14 +1001,21 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -975,7 +1296,7 @@
   <dimension ref="A1:AT169"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.3984375"/>
+    <col min="1" max="1" width="9.3984375" style="24"/>
     <col min="2" max="2" width="12.6640625" style="11"/>
     <col min="3" max="3" width="12.6640625"/>
     <col min="4" max="5" width="9" style="17"/>
@@ -983,148 +1304,148 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
-        <v>108</v>
+      <c r="A1" s="19" t="s">
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>109</v>
+        <v>2</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>110</v>
+        <v>3</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>151</v>
+        <v>44</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>152</v>
+        <v>45</v>
       </c>
       <c r="F1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>111</v>
+        <v>4</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>112</v>
+        <v>5</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>113</v>
+        <v>6</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>114</v>
+        <v>7</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>115</v>
+        <v>8</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>116</v>
+        <v>9</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>117</v>
+        <v>10</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>121</v>
+        <v>14</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>118</v>
+        <v>11</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>119</v>
+        <v>12</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>122</v>
+        <v>15</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="U1" s="9" t="s">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="V1" s="9" t="s">
-        <v>126</v>
+        <v>19</v>
       </c>
       <c r="W1" s="9" t="s">
-        <v>127</v>
+        <v>20</v>
       </c>
       <c r="X1" s="9" t="s">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="Y1" s="9" t="s">
-        <v>129</v>
+        <v>22</v>
       </c>
       <c r="Z1" s="9" t="s">
-        <v>138</v>
+        <v>31</v>
       </c>
       <c r="AA1" s="9" t="s">
-        <v>130</v>
+        <v>23</v>
       </c>
       <c r="AB1" s="9" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
       <c r="AC1" s="9" t="s">
-        <v>132</v>
+        <v>25</v>
       </c>
       <c r="AD1" s="9" t="s">
-        <v>133</v>
+        <v>26</v>
       </c>
       <c r="AE1" s="9" t="s">
-        <v>134</v>
+        <v>27</v>
       </c>
       <c r="AF1" s="9" t="s">
-        <v>135</v>
+        <v>28</v>
       </c>
       <c r="AG1" s="9" t="s">
-        <v>136</v>
+        <v>29</v>
       </c>
       <c r="AH1" s="9" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="AI1" s="9" t="s">
-        <v>139</v>
+        <v>32</v>
       </c>
       <c r="AJ1" s="9" t="s">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="AK1" s="9" t="s">
-        <v>141</v>
+        <v>34</v>
       </c>
       <c r="AL1" s="9" t="s">
-        <v>142</v>
+        <v>35</v>
       </c>
       <c r="AM1" t="s">
-        <v>143</v>
+        <v>36</v>
       </c>
       <c r="AN1" t="s">
-        <v>144</v>
+        <v>37</v>
       </c>
       <c r="AO1" t="s">
-        <v>145</v>
+        <v>38</v>
       </c>
       <c r="AP1" t="s">
-        <v>146</v>
+        <v>39</v>
       </c>
       <c r="AQ1" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
       <c r="AR1" t="s">
-        <v>148</v>
+        <v>41</v>
       </c>
       <c r="AS1" t="s">
-        <v>149</v>
+        <v>42</v>
       </c>
       <c r="AT1" t="s">
-        <v>150</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
+      <c r="A2" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="B2" s="10">
         <v>21</v>
@@ -1263,8 +1584,8 @@
       </c>
     </row>
     <row r="3" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
+      <c r="A3" s="20" t="s">
+        <v>47</v>
       </c>
       <c r="B3" s="10">
         <v>18</v>
@@ -1403,8 +1724,8 @@
       </c>
     </row>
     <row r="4" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
+      <c r="A4" s="20" t="s">
+        <v>48</v>
       </c>
       <c r="B4" s="10">
         <v>19</v>
@@ -1543,8 +1864,8 @@
       </c>
     </row>
     <row r="5" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
+      <c r="A5" s="20" t="s">
+        <v>49</v>
       </c>
       <c r="B5" s="10">
         <v>23</v>
@@ -1683,8 +2004,8 @@
       </c>
     </row>
     <row r="6" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
+      <c r="A6" s="20" t="s">
+        <v>50</v>
       </c>
       <c r="B6" s="10">
         <v>20</v>
@@ -1823,8 +2144,8 @@
       </c>
     </row>
     <row r="7" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
+      <c r="A7" s="20" t="s">
+        <v>51</v>
       </c>
       <c r="B7" s="10">
         <v>20</v>
@@ -1963,8 +2284,8 @@
       </c>
     </row>
     <row r="8" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
+      <c r="A8" s="20" t="s">
+        <v>52</v>
       </c>
       <c r="B8" s="10">
         <v>20</v>
@@ -2103,8 +2424,8 @@
       </c>
     </row>
     <row r="9" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
+      <c r="A9" s="20" t="s">
+        <v>53</v>
       </c>
       <c r="B9" s="10">
         <v>21</v>
@@ -2243,8 +2564,8 @@
       </c>
     </row>
     <row r="10" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
+      <c r="A10" s="20" t="s">
+        <v>54</v>
       </c>
       <c r="B10" s="10">
         <v>26</v>
@@ -2383,8 +2704,8 @@
       </c>
     </row>
     <row r="11" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
+      <c r="A11" s="20" t="s">
+        <v>56</v>
       </c>
       <c r="B11" s="10">
         <v>20</v>
@@ -2523,8 +2844,8 @@
       </c>
     </row>
     <row r="12" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
+      <c r="A12" s="20" t="s">
+        <v>55</v>
       </c>
       <c r="B12" s="10">
         <v>20</v>
@@ -2663,8 +2984,8 @@
       </c>
     </row>
     <row r="13" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
+      <c r="A13" s="20" t="s">
+        <v>57</v>
       </c>
       <c r="B13" s="10">
         <v>20</v>
@@ -2803,8 +3124,8 @@
       </c>
     </row>
     <row r="14" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
+      <c r="A14" s="20" t="s">
+        <v>58</v>
       </c>
       <c r="B14" s="10">
         <v>20</v>
@@ -2943,8 +3264,8 @@
       </c>
     </row>
     <row r="15" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
+      <c r="A15" s="20" t="s">
+        <v>59</v>
       </c>
       <c r="B15" s="10">
         <v>19</v>
@@ -3083,8 +3404,8 @@
       </c>
     </row>
     <row r="16" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
+      <c r="A16" s="20" t="s">
+        <v>60</v>
       </c>
       <c r="B16" s="10">
         <v>20</v>
@@ -3223,8 +3544,8 @@
       </c>
     </row>
     <row r="17" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
+      <c r="A17" s="20" t="s">
+        <v>61</v>
       </c>
       <c r="B17" s="10">
         <v>19</v>
@@ -3363,8 +3684,8 @@
       </c>
     </row>
     <row r="18" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="1" t="s">
-        <v>17</v>
+      <c r="A18" s="20" t="s">
+        <v>62</v>
       </c>
       <c r="B18" s="10">
         <v>20</v>
@@ -3503,8 +3824,8 @@
       </c>
     </row>
     <row r="19" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="1" t="s">
-        <v>2</v>
+      <c r="A19" s="20" t="s">
+        <v>63</v>
       </c>
       <c r="B19" s="10">
         <v>18</v>
@@ -3643,8 +3964,8 @@
       </c>
     </row>
     <row r="20" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="1" t="s">
-        <v>6</v>
+      <c r="A20" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="B20" s="10">
         <v>20</v>
@@ -3783,8 +4104,8 @@
       </c>
     </row>
     <row r="21" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="1" t="s">
-        <v>18</v>
+      <c r="A21" s="20" t="s">
+        <v>65</v>
       </c>
       <c r="B21" s="10">
         <v>20</v>
@@ -3923,8 +4244,8 @@
       </c>
     </row>
     <row r="22" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="3" t="s">
-        <v>19</v>
+      <c r="A22" s="21" t="s">
+        <v>66</v>
       </c>
       <c r="B22" s="10">
         <v>20</v>
@@ -4063,8 +4384,8 @@
       </c>
     </row>
     <row r="23" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="1" t="s">
-        <v>20</v>
+      <c r="A23" s="20" t="s">
+        <v>67</v>
       </c>
       <c r="B23" s="10">
         <v>19</v>
@@ -4203,8 +4524,8 @@
       </c>
     </row>
     <row r="24" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="1" t="s">
-        <v>21</v>
+      <c r="A24" s="20" t="s">
+        <v>68</v>
       </c>
       <c r="B24" s="10">
         <v>20</v>
@@ -4343,8 +4664,8 @@
       </c>
     </row>
     <row r="25" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="1" t="s">
-        <v>22</v>
+      <c r="A25" s="20" t="s">
+        <v>69</v>
       </c>
       <c r="B25" s="10">
         <v>19</v>
@@ -4483,8 +4804,8 @@
       </c>
     </row>
     <row r="26" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="1" t="s">
-        <v>23</v>
+      <c r="A26" s="20" t="s">
+        <v>70</v>
       </c>
       <c r="B26" s="10">
         <v>22</v>
@@ -4623,8 +4944,8 @@
       </c>
     </row>
     <row r="27" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="1" t="s">
-        <v>24</v>
+      <c r="A27" s="20" t="s">
+        <v>71</v>
       </c>
       <c r="B27" s="10">
         <v>19</v>
@@ -4763,8 +5084,8 @@
       </c>
     </row>
     <row r="28" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="1" t="s">
-        <v>25</v>
+      <c r="A28" s="20" t="s">
+        <v>72</v>
       </c>
       <c r="B28" s="10">
         <v>20</v>
@@ -4903,8 +5224,8 @@
       </c>
     </row>
     <row r="29" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="4">
-        <v>210</v>
+      <c r="A29" s="22" t="s">
+        <v>73</v>
       </c>
       <c r="B29" s="10">
         <v>22</v>
@@ -5043,8 +5364,8 @@
       </c>
     </row>
     <row r="30" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="4">
-        <v>20220721</v>
+      <c r="A30" s="22" t="s">
+        <v>74</v>
       </c>
       <c r="B30" s="10">
         <v>22</v>
@@ -5183,8 +5504,8 @@
       </c>
     </row>
     <row r="31" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="4" t="s">
-        <v>26</v>
+      <c r="A31" s="22" t="s">
+        <v>75</v>
       </c>
       <c r="B31" s="10">
         <v>22</v>
@@ -5323,8 +5644,8 @@
       </c>
     </row>
     <row r="32" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="4" t="s">
-        <v>27</v>
+      <c r="A32" s="22" t="s">
+        <v>76</v>
       </c>
       <c r="B32" s="10">
         <v>24</v>
@@ -5463,8 +5784,8 @@
       </c>
     </row>
     <row r="33" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="4" t="s">
-        <v>28</v>
+      <c r="A33" s="22" t="s">
+        <v>77</v>
       </c>
       <c r="B33" s="10">
         <v>22</v>
@@ -5603,8 +5924,8 @@
       </c>
     </row>
     <row r="34" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="4" t="s">
-        <v>29</v>
+      <c r="A34" s="22" t="s">
+        <v>78</v>
       </c>
       <c r="B34" s="10">
         <v>20</v>
@@ -5743,8 +6064,8 @@
       </c>
     </row>
     <row r="35" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="4" t="s">
-        <v>30</v>
+      <c r="A35" s="22" t="s">
+        <v>79</v>
       </c>
       <c r="B35" s="10">
         <v>21</v>
@@ -5883,8 +6204,8 @@
       </c>
     </row>
     <row r="36" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="4" t="s">
-        <v>31</v>
+      <c r="A36" s="22" t="s">
+        <v>80</v>
       </c>
       <c r="B36" s="10">
         <v>21</v>
@@ -6023,8 +6344,8 @@
       </c>
     </row>
     <row r="37" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="4" t="s">
-        <v>32</v>
+      <c r="A37" s="22" t="s">
+        <v>81</v>
       </c>
       <c r="B37" s="10">
         <v>22</v>
@@ -6163,8 +6484,8 @@
       </c>
     </row>
     <row r="38" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="4" t="s">
-        <v>33</v>
+      <c r="A38" s="22" t="s">
+        <v>82</v>
       </c>
       <c r="B38" s="10">
         <v>21</v>
@@ -6303,8 +6624,8 @@
       </c>
     </row>
     <row r="39" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="4" t="s">
-        <v>34</v>
+      <c r="A39" s="22" t="s">
+        <v>83</v>
       </c>
       <c r="B39" s="10">
         <v>23</v>
@@ -6443,8 +6764,8 @@
       </c>
     </row>
     <row r="40" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="1" t="s">
-        <v>1</v>
+      <c r="A40" s="20" t="s">
+        <v>84</v>
       </c>
       <c r="B40" s="10">
         <v>21</v>
@@ -6583,8 +6904,8 @@
       </c>
     </row>
     <row r="41" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="1" t="s">
-        <v>3</v>
+      <c r="A41" s="20" t="s">
+        <v>85</v>
       </c>
       <c r="B41" s="10">
         <v>19</v>
@@ -6723,8 +7044,8 @@
       </c>
     </row>
     <row r="42" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="1" t="s">
-        <v>4</v>
+      <c r="A42" s="20" t="s">
+        <v>86</v>
       </c>
       <c r="B42" s="10">
         <v>23</v>
@@ -6863,8 +7184,8 @@
       </c>
     </row>
     <row r="43" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="1" t="s">
-        <v>5</v>
+      <c r="A43" s="20" t="s">
+        <v>87</v>
       </c>
       <c r="B43" s="10">
         <v>20</v>
@@ -7003,8 +7324,8 @@
       </c>
     </row>
     <row r="44" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="1" t="s">
-        <v>6</v>
+      <c r="A44" s="20" t="s">
+        <v>88</v>
       </c>
       <c r="B44" s="10">
         <v>20</v>
@@ -7143,8 +7464,8 @@
       </c>
     </row>
     <row r="45" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="1" t="s">
-        <v>7</v>
+      <c r="A45" s="20" t="s">
+        <v>89</v>
       </c>
       <c r="B45" s="10">
         <v>20</v>
@@ -7283,8 +7604,8 @@
       </c>
     </row>
     <row r="46" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="1" t="s">
-        <v>9</v>
+      <c r="A46" s="20" t="s">
+        <v>90</v>
       </c>
       <c r="B46" s="10">
         <v>26</v>
@@ -7423,8 +7744,8 @@
       </c>
     </row>
     <row r="47" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="1" t="s">
-        <v>10</v>
+      <c r="A47" s="20" t="s">
+        <v>91</v>
       </c>
       <c r="B47" s="10">
         <v>20</v>
@@ -7563,8 +7884,8 @@
       </c>
     </row>
     <row r="48" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="1" t="s">
-        <v>11</v>
+      <c r="A48" s="20" t="s">
+        <v>92</v>
       </c>
       <c r="B48" s="10">
         <v>20</v>
@@ -7703,8 +8024,8 @@
       </c>
     </row>
     <row r="49" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="1" t="s">
-        <v>12</v>
+      <c r="A49" s="20" t="s">
+        <v>93</v>
       </c>
       <c r="B49" s="10">
         <v>20</v>
@@ -7843,8 +8164,8 @@
       </c>
     </row>
     <row r="50" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="1" t="s">
-        <v>13</v>
+      <c r="A50" s="20" t="s">
+        <v>94</v>
       </c>
       <c r="B50" s="10">
         <v>20</v>
@@ -7983,8 +8304,8 @@
       </c>
     </row>
     <row r="51" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="1" t="s">
-        <v>14</v>
+      <c r="A51" s="20" t="s">
+        <v>95</v>
       </c>
       <c r="B51" s="10">
         <v>19</v>
@@ -8123,8 +8444,8 @@
       </c>
     </row>
     <row r="52" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="1" t="s">
-        <v>15</v>
+      <c r="A52" s="20" t="s">
+        <v>96</v>
       </c>
       <c r="B52" s="10">
         <v>20</v>
@@ -8263,8 +8584,8 @@
       </c>
     </row>
     <row r="53" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="1" t="s">
-        <v>8</v>
+      <c r="A53" s="20" t="s">
+        <v>97</v>
       </c>
       <c r="B53" s="10">
         <v>21</v>
@@ -8403,8 +8724,8 @@
       </c>
     </row>
     <row r="54" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="1" t="s">
-        <v>17</v>
+      <c r="A54" s="20" t="s">
+        <v>98</v>
       </c>
       <c r="B54" s="10">
         <v>20</v>
@@ -8543,8 +8864,8 @@
       </c>
     </row>
     <row r="55" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="1" t="s">
-        <v>6</v>
+      <c r="A55" s="20" t="s">
+        <v>99</v>
       </c>
       <c r="B55" s="10">
         <v>20</v>
@@ -8683,8 +9004,8 @@
       </c>
     </row>
     <row r="56" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="1" t="s">
-        <v>35</v>
+      <c r="A56" s="20" t="s">
+        <v>100</v>
       </c>
       <c r="B56" s="10">
         <v>19</v>
@@ -8823,8 +9144,8 @@
       </c>
     </row>
     <row r="57" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="1" t="s">
-        <v>20</v>
+      <c r="A57" s="20" t="s">
+        <v>101</v>
       </c>
       <c r="B57" s="10">
         <v>19</v>
@@ -8963,8 +9284,8 @@
       </c>
     </row>
     <row r="58" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="1" t="s">
-        <v>21</v>
+      <c r="A58" s="20" t="s">
+        <v>102</v>
       </c>
       <c r="B58" s="10">
         <v>20</v>
@@ -9103,8 +9424,8 @@
       </c>
     </row>
     <row r="59" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="1" t="s">
-        <v>22</v>
+      <c r="A59" s="20" t="s">
+        <v>103</v>
       </c>
       <c r="B59" s="10">
         <v>19</v>
@@ -9243,8 +9564,8 @@
       </c>
     </row>
     <row r="60" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="1" t="s">
-        <v>23</v>
+      <c r="A60" s="20" t="s">
+        <v>104</v>
       </c>
       <c r="B60" s="10">
         <v>22</v>
@@ -9383,8 +9704,8 @@
       </c>
     </row>
     <row r="61" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="1" t="s">
-        <v>24</v>
+      <c r="A61" s="20" t="s">
+        <v>105</v>
       </c>
       <c r="B61" s="10">
         <v>19</v>
@@ -9523,8 +9844,8 @@
       </c>
     </row>
     <row r="62" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="1" t="s">
-        <v>25</v>
+      <c r="A62" s="20" t="s">
+        <v>106</v>
       </c>
       <c r="B62" s="10">
         <v>20</v>
@@ -9663,8 +9984,8 @@
       </c>
     </row>
     <row r="63" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="1" t="s">
-        <v>18</v>
+      <c r="A63" s="20" t="s">
+        <v>107</v>
       </c>
       <c r="B63" s="10">
         <v>20</v>
@@ -9803,8 +10124,8 @@
       </c>
     </row>
     <row r="64" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="1" t="s">
-        <v>36</v>
+      <c r="A64" s="20" t="s">
+        <v>108</v>
       </c>
       <c r="B64" s="11">
         <v>20</v>
@@ -9943,8 +10264,8 @@
       </c>
     </row>
     <row r="65" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="1" t="s">
-        <v>37</v>
+      <c r="A65" s="20" t="s">
+        <v>109</v>
       </c>
       <c r="B65" s="11">
         <v>21</v>
@@ -10083,8 +10404,8 @@
       </c>
     </row>
     <row r="66" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="1" t="s">
-        <v>38</v>
+      <c r="A66" s="20" t="s">
+        <v>110</v>
       </c>
       <c r="B66" s="11">
         <v>20</v>
@@ -10223,8 +10544,8 @@
       </c>
     </row>
     <row r="67" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="1" t="s">
-        <v>39</v>
+      <c r="A67" s="20" t="s">
+        <v>111</v>
       </c>
       <c r="B67" s="11">
         <v>21</v>
@@ -10363,8 +10684,8 @@
       </c>
     </row>
     <row r="68" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="1" t="s">
-        <v>40</v>
+      <c r="A68" s="20" t="s">
+        <v>112</v>
       </c>
       <c r="B68" s="11">
         <v>20</v>
@@ -10503,8 +10824,8 @@
       </c>
     </row>
     <row r="69" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="1" t="s">
-        <v>41</v>
+      <c r="A69" s="20" t="s">
+        <v>113</v>
       </c>
       <c r="B69" s="11">
         <v>21</v>
@@ -10643,8 +10964,8 @@
       </c>
     </row>
     <row r="70" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="1" t="s">
-        <v>42</v>
+      <c r="A70" s="20" t="s">
+        <v>114</v>
       </c>
       <c r="B70" s="11">
         <v>21</v>
@@ -10783,8 +11104,8 @@
       </c>
     </row>
     <row r="71" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="1" t="s">
-        <v>43</v>
+      <c r="A71" s="20" t="s">
+        <v>115</v>
       </c>
       <c r="B71" s="11">
         <v>21</v>
@@ -10923,8 +11244,8 @@
       </c>
     </row>
     <row r="72" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="1" t="s">
-        <v>44</v>
+      <c r="A72" s="20" t="s">
+        <v>116</v>
       </c>
       <c r="B72" s="11">
         <v>21</v>
@@ -11063,8 +11384,8 @@
       </c>
     </row>
     <row r="73" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="1" t="s">
-        <v>33</v>
+      <c r="A73" s="20" t="s">
+        <v>117</v>
       </c>
       <c r="B73" s="11">
         <v>21</v>
@@ -11203,8 +11524,8 @@
       </c>
     </row>
     <row r="74" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="1" t="s">
-        <v>22</v>
+      <c r="A74" s="20" t="s">
+        <v>118</v>
       </c>
       <c r="B74" s="11">
         <v>21</v>
@@ -11343,8 +11664,8 @@
       </c>
     </row>
     <row r="75" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="1" t="s">
-        <v>45</v>
+      <c r="A75" s="20" t="s">
+        <v>119</v>
       </c>
       <c r="B75" s="11">
         <v>20</v>
@@ -11483,8 +11804,8 @@
       </c>
     </row>
     <row r="76" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="1" t="s">
-        <v>46</v>
+      <c r="A76" s="20" t="s">
+        <v>120</v>
       </c>
       <c r="B76" s="11">
         <v>22</v>
@@ -11623,8 +11944,8 @@
       </c>
     </row>
     <row r="77" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="1" t="s">
-        <v>47</v>
+      <c r="A77" s="20" t="s">
+        <v>121</v>
       </c>
       <c r="B77" s="12">
         <v>20</v>
@@ -11763,8 +12084,8 @@
       </c>
     </row>
     <row r="78" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="6" t="s">
-        <v>48</v>
+      <c r="A78" s="23" t="s">
+        <v>122</v>
       </c>
       <c r="B78" s="12">
         <v>22</v>
@@ -11899,8 +12220,8 @@
       </c>
     </row>
     <row r="79" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="6" t="s">
-        <v>49</v>
+      <c r="A79" s="23" t="s">
+        <v>123</v>
       </c>
       <c r="B79" s="12">
         <v>23</v>
@@ -12038,149 +12359,149 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="80" spans="1:46" s="19" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="B80" s="20">
+    <row r="80" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B80" s="10">
         <v>21</v>
       </c>
-      <c r="C80" s="20">
-        <v>1</v>
-      </c>
-      <c r="D80" s="21">
+      <c r="C80" s="10">
+        <v>1</v>
+      </c>
+      <c r="D80" s="18">
         <v>4</v>
       </c>
-      <c r="E80" s="21">
+      <c r="E80" s="18">
         <v>3</v>
       </c>
-      <c r="F80" s="20">
+      <c r="F80" s="10">
         <v>3</v>
       </c>
-      <c r="G80" s="20">
+      <c r="G80" s="10">
         <v>25</v>
       </c>
-      <c r="H80" s="19">
+      <c r="H80" s="1">
         <v>75</v>
       </c>
-      <c r="I80" s="19">
+      <c r="I80" s="3">
         <v>70</v>
       </c>
-      <c r="J80" s="19">
-        <v>0</v>
-      </c>
-      <c r="K80" s="19">
-        <v>2</v>
-      </c>
-      <c r="L80" s="19">
-        <v>1</v>
-      </c>
-      <c r="M80" s="19">
+      <c r="J80" s="3">
+        <v>0</v>
+      </c>
+      <c r="K80" s="1">
+        <v>2</v>
+      </c>
+      <c r="L80" s="3">
+        <v>1</v>
+      </c>
+      <c r="M80" s="1">
         <v>5.83</v>
       </c>
-      <c r="N80" s="19">
+      <c r="N80" s="1">
         <v>2.36</v>
       </c>
-      <c r="O80" s="19">
+      <c r="O80" s="1">
         <v>0.32</v>
       </c>
-      <c r="P80" s="19">
+      <c r="P80" s="1">
         <v>0.42</v>
       </c>
-      <c r="Q80" s="19">
+      <c r="Q80" s="1">
         <v>0.37</v>
       </c>
-      <c r="R80" s="19">
+      <c r="R80" s="1">
         <v>0.11</v>
       </c>
-      <c r="S80" s="19">
+      <c r="S80" s="1">
         <v>0.44</v>
       </c>
-      <c r="T80" s="19">
+      <c r="T80" s="1">
         <v>8.6300000000000008</v>
       </c>
-      <c r="U80" s="19">
+      <c r="U80" s="1">
         <v>0.87</v>
       </c>
-      <c r="V80" s="19">
+      <c r="V80" s="1">
         <v>0.1</v>
       </c>
-      <c r="W80" s="19">
+      <c r="W80" s="1">
         <v>0.15</v>
       </c>
-      <c r="X80" s="19">
+      <c r="X80" s="1">
         <v>0.11</v>
       </c>
-      <c r="Y80" s="19">
+      <c r="Y80" s="1">
         <v>0.14000000000000001</v>
       </c>
-      <c r="Z80" s="19">
+      <c r="Z80" s="1">
         <v>0.22</v>
       </c>
-      <c r="AA80" s="19">
+      <c r="AA80" s="1">
         <v>-0.24</v>
       </c>
-      <c r="AB80" s="19">
+      <c r="AB80" s="1">
         <v>-0.12</v>
       </c>
-      <c r="AC80" s="19">
+      <c r="AC80" s="1">
         <v>-0.24</v>
       </c>
-      <c r="AD80" s="19">
+      <c r="AD80" s="1">
         <v>-0.36</v>
       </c>
-      <c r="AE80" s="19">
+      <c r="AE80" s="1">
         <v>40</v>
       </c>
-      <c r="AF80" s="19">
+      <c r="AF80" s="1">
         <v>30</v>
       </c>
-      <c r="AG80" s="19">
+      <c r="AG80" s="1">
         <v>0.4</v>
       </c>
-      <c r="AH80" s="19">
+      <c r="AH80" s="1">
         <v>0.3</v>
       </c>
-      <c r="AI80" s="19">
+      <c r="AI80" s="1">
         <v>0.28000000000000003</v>
       </c>
-      <c r="AJ80" s="19">
+      <c r="AJ80" s="1">
         <v>-0.08</v>
       </c>
-      <c r="AK80" s="19">
+      <c r="AK80" s="1">
         <v>-0.09</v>
       </c>
-      <c r="AL80" s="19">
-        <v>0</v>
-      </c>
-      <c r="AM80" s="19">
+      <c r="AL80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM80" s="14">
         <v>0.92</v>
       </c>
-      <c r="AN80" s="19">
+      <c r="AN80" s="14">
         <v>0.7</v>
       </c>
-      <c r="AO80" s="19">
+      <c r="AO80" s="14">
         <v>0.64</v>
       </c>
-      <c r="AP80" s="19">
+      <c r="AP80" s="14">
         <v>0.78</v>
       </c>
-      <c r="AQ80" s="19">
+      <c r="AQ80" s="14">
         <v>0.81</v>
       </c>
-      <c r="AR80" s="19">
+      <c r="AR80" s="14">
         <v>0.75</v>
       </c>
-      <c r="AS80" s="19">
+      <c r="AS80" s="14">
         <v>0.9</v>
       </c>
-      <c r="AT80" s="19">
+      <c r="AT80" s="14">
         <v>0.75</v>
       </c>
     </row>
     <row r="81" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="6" t="s">
-        <v>51</v>
+      <c r="A81" s="23" t="s">
+        <v>125</v>
       </c>
       <c r="B81" s="12">
         <v>18</v>
@@ -12315,8 +12636,8 @@
       </c>
     </row>
     <row r="82" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="6" t="s">
-        <v>52</v>
+      <c r="A82" s="23" t="s">
+        <v>126</v>
       </c>
       <c r="B82" s="12">
         <v>20</v>
@@ -12455,8 +12776,8 @@
       </c>
     </row>
     <row r="83" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="6" t="s">
-        <v>53</v>
+      <c r="A83" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="B83" s="12">
         <v>21</v>
@@ -12595,8 +12916,8 @@
       </c>
     </row>
     <row r="84" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="6" t="s">
-        <v>54</v>
+      <c r="A84" s="23" t="s">
+        <v>128</v>
       </c>
       <c r="B84" s="12">
         <v>22</v>
@@ -12735,8 +13056,8 @@
       </c>
     </row>
     <row r="85" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="6" t="s">
-        <v>55</v>
+      <c r="A85" s="23" t="s">
+        <v>129</v>
       </c>
       <c r="B85" s="12">
         <v>20</v>
@@ -12875,8 +13196,8 @@
       </c>
     </row>
     <row r="86" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="6" t="s">
-        <v>56</v>
+      <c r="A86" s="23" t="s">
+        <v>130</v>
       </c>
       <c r="B86" s="12">
         <v>23</v>
@@ -13011,8 +13332,8 @@
       </c>
     </row>
     <row r="87" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="6" t="s">
-        <v>57</v>
+      <c r="A87" s="23" t="s">
+        <v>131</v>
       </c>
       <c r="B87" s="12">
         <v>23</v>
@@ -13151,8 +13472,8 @@
       </c>
     </row>
     <row r="88" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="6" t="s">
-        <v>58</v>
+      <c r="A88" s="23" t="s">
+        <v>132</v>
       </c>
       <c r="B88" s="12">
         <v>20</v>
@@ -13291,8 +13612,8 @@
       </c>
     </row>
     <row r="89" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="6" t="s">
-        <v>59</v>
+      <c r="A89" s="23" t="s">
+        <v>133</v>
       </c>
       <c r="B89" s="12">
         <v>27</v>
@@ -13431,8 +13752,8 @@
       </c>
     </row>
     <row r="90" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="6" t="s">
-        <v>60</v>
+      <c r="A90" s="23" t="s">
+        <v>134</v>
       </c>
       <c r="B90" s="12">
         <v>20</v>
@@ -13571,8 +13892,8 @@
       </c>
     </row>
     <row r="91" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="6" t="s">
-        <v>61</v>
+      <c r="A91" s="23" t="s">
+        <v>135</v>
       </c>
       <c r="B91" s="12">
         <v>19</v>
@@ -13711,8 +14032,8 @@
       </c>
     </row>
     <row r="92" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="6" t="s">
-        <v>62</v>
+      <c r="A92" s="23" t="s">
+        <v>136</v>
       </c>
       <c r="B92" s="12">
         <v>19</v>
@@ -13851,8 +14172,8 @@
       </c>
     </row>
     <row r="93" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="6" t="s">
-        <v>63</v>
+      <c r="A93" s="23" t="s">
+        <v>137</v>
       </c>
       <c r="B93" s="10">
         <v>19</v>
@@ -13991,8 +14312,8 @@
       </c>
     </row>
     <row r="94" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="6" t="s">
-        <v>64</v>
+      <c r="A94" s="23" t="s">
+        <v>138</v>
       </c>
       <c r="B94" s="12">
         <v>20</v>
@@ -14131,8 +14452,8 @@
       </c>
     </row>
     <row r="95" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="1" t="s">
-        <v>65</v>
+      <c r="A95" s="20" t="s">
+        <v>139</v>
       </c>
       <c r="B95" s="12">
         <v>21</v>
@@ -14271,8 +14592,8 @@
       </c>
     </row>
     <row r="96" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="1" t="s">
-        <v>66</v>
+      <c r="A96" s="20" t="s">
+        <v>140</v>
       </c>
       <c r="B96" s="12">
         <v>22</v>
@@ -14407,8 +14728,8 @@
       </c>
     </row>
     <row r="97" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A97" s="1" t="s">
-        <v>67</v>
+      <c r="A97" s="20" t="s">
+        <v>141</v>
       </c>
       <c r="B97" s="12">
         <v>23</v>
@@ -14547,8 +14868,8 @@
       </c>
     </row>
     <row r="98" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="1" t="s">
-        <v>68</v>
+      <c r="A98" s="20" t="s">
+        <v>142</v>
       </c>
       <c r="B98" s="12">
         <v>18</v>
@@ -14687,8 +15008,8 @@
       </c>
     </row>
     <row r="99" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A99" s="1" t="s">
-        <v>44</v>
+      <c r="A99" s="20" t="s">
+        <v>143</v>
       </c>
       <c r="B99" s="12">
         <v>20</v>
@@ -14827,8 +15148,8 @@
       </c>
     </row>
     <row r="100" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A100" s="1" t="s">
-        <v>69</v>
+      <c r="A100" s="20" t="s">
+        <v>144</v>
       </c>
       <c r="B100" s="12">
         <v>22</v>
@@ -14967,8 +15288,8 @@
       </c>
     </row>
     <row r="101" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A101" s="1" t="s">
-        <v>70</v>
+      <c r="A101" s="20" t="s">
+        <v>145</v>
       </c>
       <c r="B101" s="12">
         <v>23</v>
@@ -15107,8 +15428,8 @@
       </c>
     </row>
     <row r="102" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A102" s="1" t="s">
-        <v>71</v>
+      <c r="A102" s="20" t="s">
+        <v>146</v>
       </c>
       <c r="B102" s="11">
         <v>23</v>
@@ -15247,8 +15568,8 @@
       </c>
     </row>
     <row r="103" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A103" s="1" t="s">
-        <v>72</v>
+      <c r="A103" s="20" t="s">
+        <v>147</v>
       </c>
       <c r="B103" s="11">
         <v>23</v>
@@ -15387,8 +15708,8 @@
       </c>
     </row>
     <row r="104" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="1" t="s">
-        <v>73</v>
+      <c r="A104" s="20" t="s">
+        <v>148</v>
       </c>
       <c r="B104" s="11">
         <v>22</v>
@@ -15527,8 +15848,8 @@
       </c>
     </row>
     <row r="105" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A105" s="1" t="s">
-        <v>74</v>
+      <c r="A105" s="20" t="s">
+        <v>149</v>
       </c>
       <c r="B105" s="11">
         <v>23</v>
@@ -15667,8 +15988,8 @@
       </c>
     </row>
     <row r="106" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A106" s="1" t="s">
-        <v>48</v>
+      <c r="A106" s="20" t="s">
+        <v>150</v>
       </c>
       <c r="B106" s="11">
         <v>22</v>
@@ -15807,8 +16128,8 @@
       </c>
     </row>
     <row r="107" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="1" t="s">
-        <v>75</v>
+      <c r="A107" s="20" t="s">
+        <v>151</v>
       </c>
       <c r="B107" s="11">
         <v>22</v>
@@ -15947,8 +16268,8 @@
       </c>
     </row>
     <row r="108" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A108" s="1" t="s">
-        <v>76</v>
+      <c r="A108" s="20" t="s">
+        <v>152</v>
       </c>
       <c r="B108" s="11">
         <v>19</v>
@@ -16087,8 +16408,8 @@
       </c>
     </row>
     <row r="109" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A109" s="1" t="s">
-        <v>77</v>
+      <c r="A109" s="20" t="s">
+        <v>153</v>
       </c>
       <c r="B109" s="11">
         <v>21</v>
@@ -16227,8 +16548,8 @@
       </c>
     </row>
     <row r="110" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="1" t="s">
-        <v>78</v>
+      <c r="A110" s="20" t="s">
+        <v>154</v>
       </c>
       <c r="B110" s="11">
         <v>22</v>
@@ -16367,8 +16688,8 @@
       </c>
     </row>
     <row r="111" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A111" s="1" t="s">
-        <v>79</v>
+      <c r="A111" s="20" t="s">
+        <v>155</v>
       </c>
       <c r="B111" s="11">
         <v>22</v>
@@ -16507,8 +16828,8 @@
       </c>
     </row>
     <row r="112" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A112" s="1" t="s">
-        <v>80</v>
+      <c r="A112" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="B112" s="11">
         <v>24</v>
@@ -16647,8 +16968,8 @@
       </c>
     </row>
     <row r="113" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A113" s="1" t="s">
-        <v>81</v>
+      <c r="A113" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="B113" s="11">
         <v>22</v>
@@ -16787,8 +17108,8 @@
       </c>
     </row>
     <row r="114" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A114" s="1" t="s">
-        <v>82</v>
+      <c r="A114" s="20" t="s">
+        <v>158</v>
       </c>
       <c r="B114" s="11">
         <v>21</v>
@@ -16927,8 +17248,8 @@
       </c>
     </row>
     <row r="115" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A115" s="1" t="s">
-        <v>83</v>
+      <c r="A115" s="20" t="s">
+        <v>159</v>
       </c>
       <c r="B115" s="12">
         <v>23</v>
@@ -17067,8 +17388,8 @@
       </c>
     </row>
     <row r="116" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A116" s="1" t="s">
-        <v>84</v>
+      <c r="A116" s="20" t="s">
+        <v>160</v>
       </c>
       <c r="B116" s="11">
         <v>22</v>
@@ -17207,8 +17528,8 @@
       </c>
     </row>
     <row r="117" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A117" s="1" t="s">
-        <v>85</v>
+      <c r="A117" s="20" t="s">
+        <v>161</v>
       </c>
       <c r="B117" s="11">
         <v>21</v>
@@ -17347,8 +17668,8 @@
       </c>
     </row>
     <row r="118" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A118" s="1" t="s">
-        <v>86</v>
+      <c r="A118" s="20" t="s">
+        <v>162</v>
       </c>
       <c r="B118" s="11">
         <v>23</v>
@@ -17487,8 +17808,8 @@
       </c>
     </row>
     <row r="119" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A119" s="6" t="s">
-        <v>48</v>
+      <c r="A119" s="23" t="s">
+        <v>163</v>
       </c>
       <c r="B119" s="12">
         <v>22</v>
@@ -17623,8 +17944,8 @@
       </c>
     </row>
     <row r="120" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A120" s="6" t="s">
-        <v>49</v>
+      <c r="A120" s="23" t="s">
+        <v>164</v>
       </c>
       <c r="B120" s="12">
         <v>23</v>
@@ -17763,8 +18084,8 @@
       </c>
     </row>
     <row r="121" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A121" s="6" t="s">
-        <v>87</v>
+      <c r="A121" s="23" t="s">
+        <v>165</v>
       </c>
       <c r="B121" s="10">
         <v>21</v>
@@ -17903,8 +18224,8 @@
       </c>
     </row>
     <row r="122" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A122" s="6" t="s">
-        <v>52</v>
+      <c r="A122" s="23" t="s">
+        <v>166</v>
       </c>
       <c r="B122" s="12">
         <v>20</v>
@@ -18043,8 +18364,8 @@
       </c>
     </row>
     <row r="123" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A123" s="6" t="s">
-        <v>53</v>
+      <c r="A123" s="23" t="s">
+        <v>167</v>
       </c>
       <c r="B123" s="12">
         <v>21</v>
@@ -18183,8 +18504,8 @@
       </c>
     </row>
     <row r="124" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A124" s="6" t="s">
-        <v>88</v>
+      <c r="A124" s="23" t="s">
+        <v>168</v>
       </c>
       <c r="B124" s="12">
         <v>22</v>
@@ -18319,8 +18640,8 @@
       </c>
     </row>
     <row r="125" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A125" s="6" t="s">
-        <v>55</v>
+      <c r="A125" s="23" t="s">
+        <v>169</v>
       </c>
       <c r="B125" s="12">
         <v>20</v>
@@ -18459,8 +18780,8 @@
       </c>
     </row>
     <row r="126" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="6" t="s">
-        <v>56</v>
+      <c r="A126" s="23" t="s">
+        <v>170</v>
       </c>
       <c r="B126" s="12">
         <v>23</v>
@@ -18595,8 +18916,8 @@
       </c>
     </row>
     <row r="127" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A127" s="6" t="s">
-        <v>57</v>
+      <c r="A127" s="23" t="s">
+        <v>171</v>
       </c>
       <c r="B127" s="12">
         <v>23</v>
@@ -18735,8 +19056,8 @@
       </c>
     </row>
     <row r="128" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="6" t="s">
-        <v>58</v>
+      <c r="A128" s="23" t="s">
+        <v>172</v>
       </c>
       <c r="B128" s="12">
         <v>20</v>
@@ -18875,8 +19196,8 @@
       </c>
     </row>
     <row r="129" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A129" s="6" t="s">
-        <v>59</v>
+      <c r="A129" s="23" t="s">
+        <v>173</v>
       </c>
       <c r="B129" s="12">
         <v>27</v>
@@ -19015,8 +19336,8 @@
       </c>
     </row>
     <row r="130" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A130" s="6" t="s">
-        <v>60</v>
+      <c r="A130" s="23" t="s">
+        <v>174</v>
       </c>
       <c r="B130" s="12">
         <v>20</v>
@@ -19155,8 +19476,8 @@
       </c>
     </row>
     <row r="131" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A131" s="6" t="s">
-        <v>61</v>
+      <c r="A131" s="23" t="s">
+        <v>175</v>
       </c>
       <c r="B131" s="12">
         <v>19</v>
@@ -19295,8 +19616,8 @@
       </c>
     </row>
     <row r="132" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A132" s="6" t="s">
-        <v>62</v>
+      <c r="A132" s="23" t="s">
+        <v>176</v>
       </c>
       <c r="B132" s="12">
         <v>19</v>
@@ -19435,8 +19756,8 @@
       </c>
     </row>
     <row r="133" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A133" s="6" t="s">
-        <v>63</v>
+      <c r="A133" s="23" t="s">
+        <v>177</v>
       </c>
       <c r="B133" s="10">
         <v>19</v>
@@ -19575,8 +19896,8 @@
       </c>
     </row>
     <row r="134" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A134" s="6" t="s">
-        <v>64</v>
+      <c r="A134" s="23" t="s">
+        <v>178</v>
       </c>
       <c r="B134" s="12">
         <v>20</v>
@@ -19715,8 +20036,8 @@
       </c>
     </row>
     <row r="135" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A135" s="6" t="s">
-        <v>54</v>
+      <c r="A135" s="23" t="s">
+        <v>179</v>
       </c>
       <c r="B135" s="12">
         <v>22</v>
@@ -19855,8 +20176,8 @@
       </c>
     </row>
     <row r="136" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A136" s="1" t="s">
-        <v>65</v>
+      <c r="A136" s="20" t="s">
+        <v>180</v>
       </c>
       <c r="B136" s="12">
         <v>21</v>
@@ -19995,8 +20316,8 @@
       </c>
     </row>
     <row r="137" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="1" t="s">
-        <v>66</v>
+      <c r="A137" s="20" t="s">
+        <v>181</v>
       </c>
       <c r="B137" s="12">
         <v>22</v>
@@ -20131,8 +20452,8 @@
       </c>
     </row>
     <row r="138" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A138" s="1" t="s">
-        <v>67</v>
+      <c r="A138" s="20" t="s">
+        <v>182</v>
       </c>
       <c r="B138" s="12">
         <v>23</v>
@@ -20271,8 +20592,8 @@
       </c>
     </row>
     <row r="139" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A139" s="1" t="s">
-        <v>68</v>
+      <c r="A139" s="20" t="s">
+        <v>183</v>
       </c>
       <c r="B139" s="12">
         <v>18</v>
@@ -20411,8 +20732,8 @@
       </c>
     </row>
     <row r="140" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A140" s="1" t="s">
-        <v>44</v>
+      <c r="A140" s="20" t="s">
+        <v>184</v>
       </c>
       <c r="B140" s="12">
         <v>20</v>
@@ -20551,8 +20872,8 @@
       </c>
     </row>
     <row r="141" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="1" t="s">
-        <v>89</v>
+      <c r="A141" s="20" t="s">
+        <v>185</v>
       </c>
       <c r="B141" s="12">
         <v>22</v>
@@ -20687,8 +21008,8 @@
       </c>
     </row>
     <row r="142" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A142" s="1" t="s">
-        <v>69</v>
+      <c r="A142" s="20" t="s">
+        <v>186</v>
       </c>
       <c r="B142" s="12">
         <v>22</v>
@@ -20827,8 +21148,8 @@
       </c>
     </row>
     <row r="143" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A143" s="1" t="s">
-        <v>70</v>
+      <c r="A143" s="20" t="s">
+        <v>187</v>
       </c>
       <c r="B143" s="12">
         <v>23</v>
@@ -20967,8 +21288,8 @@
       </c>
     </row>
     <row r="144" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A144" s="1" t="s">
-        <v>33</v>
+      <c r="A144" s="20" t="s">
+        <v>188</v>
       </c>
       <c r="B144" s="12">
         <v>19</v>
@@ -21107,8 +21428,8 @@
       </c>
     </row>
     <row r="145" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A145" s="1" t="s">
-        <v>90</v>
+      <c r="A145" s="20" t="s">
+        <v>189</v>
       </c>
       <c r="B145" s="11">
         <v>22</v>
@@ -21247,8 +21568,8 @@
       </c>
     </row>
     <row r="146" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A146" s="4" t="s">
-        <v>91</v>
+      <c r="A146" s="22" t="s">
+        <v>190</v>
       </c>
       <c r="B146" s="11">
         <v>20</v>
@@ -21387,8 +21708,8 @@
       </c>
     </row>
     <row r="147" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A147" s="4">
-        <v>1</v>
+      <c r="A147" s="22" t="s">
+        <v>191</v>
       </c>
       <c r="B147" s="11">
         <v>22</v>
@@ -21527,8 +21848,8 @@
       </c>
     </row>
     <row r="148" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A148" s="1" t="s">
-        <v>92</v>
+      <c r="A148" s="20" t="s">
+        <v>192</v>
       </c>
       <c r="B148" s="11">
         <v>24</v>
@@ -21667,8 +21988,8 @@
       </c>
     </row>
     <row r="149" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A149" s="1" t="s">
-        <v>93</v>
+      <c r="A149" s="20" t="s">
+        <v>193</v>
       </c>
       <c r="B149" s="11">
         <v>21</v>
@@ -21807,8 +22128,8 @@
       </c>
     </row>
     <row r="150" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A150" s="1" t="s">
-        <v>94</v>
+      <c r="A150" s="20" t="s">
+        <v>194</v>
       </c>
       <c r="B150" s="11">
         <v>21</v>
@@ -21947,8 +22268,8 @@
       </c>
     </row>
     <row r="151" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A151" s="1" t="s">
-        <v>95</v>
+      <c r="A151" s="20" t="s">
+        <v>195</v>
       </c>
       <c r="B151" s="11">
         <v>19</v>
@@ -22087,8 +22408,8 @@
       </c>
     </row>
     <row r="152" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="1" t="s">
-        <v>96</v>
+      <c r="A152" s="20" t="s">
+        <v>196</v>
       </c>
       <c r="B152" s="11">
         <v>21</v>
@@ -22227,8 +22548,8 @@
       </c>
     </row>
     <row r="153" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A153" s="1" t="s">
-        <v>97</v>
+      <c r="A153" s="20" t="s">
+        <v>197</v>
       </c>
       <c r="B153" s="11">
         <v>24</v>
@@ -22367,8 +22688,8 @@
       </c>
     </row>
     <row r="154" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A154" s="1" t="s">
-        <v>98</v>
+      <c r="A154" s="20" t="s">
+        <v>198</v>
       </c>
       <c r="B154" s="11">
         <v>19</v>
@@ -22507,8 +22828,8 @@
       </c>
     </row>
     <row r="155" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A155" s="1" t="s">
-        <v>99</v>
+      <c r="A155" s="20" t="s">
+        <v>199</v>
       </c>
       <c r="B155" s="11">
         <v>23</v>
@@ -22647,8 +22968,8 @@
       </c>
     </row>
     <row r="156" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A156" s="1" t="s">
-        <v>100</v>
+      <c r="A156" s="20" t="s">
+        <v>200</v>
       </c>
       <c r="B156" s="11">
         <v>19</v>
@@ -22787,8 +23108,8 @@
       </c>
     </row>
     <row r="157" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A157" s="1" t="s">
-        <v>101</v>
+      <c r="A157" s="20" t="s">
+        <v>201</v>
       </c>
       <c r="B157" s="11">
         <v>22</v>
@@ -22927,8 +23248,8 @@
       </c>
     </row>
     <row r="158" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A158" s="1" t="s">
-        <v>102</v>
+      <c r="A158" s="20" t="s">
+        <v>202</v>
       </c>
       <c r="B158" s="11">
         <v>20</v>
@@ -23067,8 +23388,8 @@
       </c>
     </row>
     <row r="159" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A159" s="1" t="s">
-        <v>103</v>
+      <c r="A159" s="20" t="s">
+        <v>203</v>
       </c>
       <c r="B159" s="11">
         <v>22</v>
@@ -23207,8 +23528,8 @@
       </c>
     </row>
     <row r="160" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="1" t="s">
-        <v>104</v>
+      <c r="A160" s="20" t="s">
+        <v>204</v>
       </c>
       <c r="B160" s="11">
         <v>22</v>
@@ -23347,8 +23668,8 @@
       </c>
     </row>
     <row r="161" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A161" s="1" t="s">
-        <v>105</v>
+      <c r="A161" s="20" t="s">
+        <v>205</v>
       </c>
       <c r="B161" s="11">
         <v>22</v>
@@ -23487,8 +23808,8 @@
       </c>
     </row>
     <row r="162" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A162" s="1" t="s">
-        <v>106</v>
+      <c r="A162" s="20" t="s">
+        <v>206</v>
       </c>
       <c r="B162" s="11">
         <v>23</v>
@@ -23627,8 +23948,8 @@
       </c>
     </row>
     <row r="163" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A163" s="1" t="s">
-        <v>107</v>
+      <c r="A163" s="20" t="s">
+        <v>207</v>
       </c>
       <c r="B163" s="11">
         <v>21</v>
@@ -23767,6 +24088,7 @@
       </c>
     </row>
     <row r="164" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A164" s="20"/>
       <c r="B164" s="10"/>
       <c r="D164" s="15"/>
       <c r="E164" s="15"/>
@@ -23782,7 +24104,7 @@
       <c r="AT164" s="14"/>
     </row>
     <row r="165" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A165"/>
+      <c r="A165" s="24"/>
       <c r="B165" s="11"/>
       <c r="C165" s="7"/>
       <c r="D165" s="17"/>
@@ -23799,7 +24121,7 @@
       <c r="AT165" s="14"/>
     </row>
     <row r="166" spans="1:46" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A166"/>
+      <c r="A166" s="24"/>
       <c r="B166" s="11"/>
       <c r="C166" s="7"/>
       <c r="D166" s="17"/>
